--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.7.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.7.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.7.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.7.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y51"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -589,7 +589,11 @@
           <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00126_19130805\oocihm.N_00126_19130805.7.txt</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr"/>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>L78: suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix), 98c (letter/digit mix) | possible duplicated/overlap line with previous line (similarity 62%) :: Ladies Underskirts, Special at 79c., 89c., 98c., $ 1.00, $ 1.10</t>
+        </is>
+      </c>
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -613,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix) :: Ladiesâ€™ White Princess Slips, Special at 79c., 89c. and $1.69.</t>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: symbol-only separator/garbage line :: 378.</t>
@@ -630,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -640,7 +648,7 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” TO ---</t>
+          <t>L107: punctuation artifact: double/multiple hyphen :: — TO ---</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr">
@@ -650,7 +658,7 @@
       </c>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with digit/letter garbage token | suspicious token(s): 0Photo (letter/digit mix) :: 0Photoâ€™s COPHRIETESLIN 6^</t>
+          <t>L289: line starts with digit/letter garbage token | suspicious token(s): 0Photo’s (letter/digit mix) :: 0Photo’s COPHRIETESLIN 6^</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -685,7 +693,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>668</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -708,12 +716,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Shop early Thursday morningâ€”Store closes at o'clock.</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+00D7 MULTIPLICATION SIGN | isolated marker/symbol line :: ×</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -773,7 +781,11 @@
       </c>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
-      <c r="F4" s="1" t="inlineStr"/>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>L769: candidate OCR token mismatch vs other OCR: "held" vs "hold" :: trade merely that they should be held.</t>
+        </is>
+      </c>
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr">
         <is>
@@ -787,12 +799,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -810,7 +822,7 @@
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”DENTI STS. ------</t>
+          <t>L231: punctuation artifact: double/multiple hyphen :: —DENTI STS. ------</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -838,21 +850,25 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>75</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
       <c r="E5" s="1" t="inlineStr"/>
-      <c r="F5" s="1" t="inlineStr"/>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>L775: candidate OCR token mismatch vs other OCR: "Imany" vs "many" :: Imany nations, bringing their knowledge-</t>
+        </is>
+      </c>
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix) :: Ladiesâ€™ White Princess Slips, Special at 79c., 89c. and $1.69.</t>
+          <t>L77: suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix) :: Ladies’ White Princess Slips, Special at 79c., 89c. and $1.69.</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
@@ -862,12 +878,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WANTED â€” TO</t>
+          <t>L323: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。''</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -891,7 +907,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L923: line starts with lowercase prefix glued to capitalized word | suspicious token(s): nJinternational (odd internal casing) | missing space after period :: nJinternational point of view.It assists to</t>
+          <t>L487: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • week,</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -927,7 +943,7 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>L78: suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix), 98c (letter/digit mix) :: Ladies Underskirts, Special at 79c., 89c., 98c., $ 1.00, $ 1.10</t>
+          <t>L78: suspicious token(s): 79c (letter/digit mix), 89c (letter/digit mix), 98c (letter/digit mix) | possible duplicated/overlap line with previous line (similarity 62%) :: Ladies Underskirts, Special at 79c., 89c., 98c., $ 1.00, $ 1.10</t>
         </is>
       </c>
       <c r="I6" s="1" t="inlineStr">
@@ -937,12 +953,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ply at Gleaner Office.â€” 634d.</t>
+          <t>L353: stray/suspicious non-ASCII glyph(s): U+95E8 CJK UNIFIED IDEOGRAPH-95E8 | isolated marker/symbol line :: 门</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -960,11 +976,15 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: hall; then he looked up and saw her -------------â€”â€”</t>
+          <t>L826: punctuation artifact: double/multiple hyphen :: hall; then he looked up and saw her -------------——</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L923: line starts with lowercase prefix glued to capitalized word | suspicious token(s): nJinternational (odd internal casing) | missing space after period :: nJinternational point of view.It assists to</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr">
@@ -984,7 +1004,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -1003,17 +1023,17 @@
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with digit/letter garbage token | suspicious token(s): 0Photo (letter/digit mix) :: 0Photoâ€™s COPHRIETESLIN 6^</t>
+          <t>L289: line starts with digit/letter garbage token | suspicious token(s): 0Photo’s (letter/digit mix) :: 0Photo’s COPHRIETESLIN 6^</t>
         </is>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: They are unapproachable â€” even</t>
+          <t>L433: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” TO ---</t>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1025,7 +1045,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -1047,7 +1067,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -1071,12 +1091,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L323: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€‚''</t>
+          <t>L761: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): BOaRd (odd internal casing) :: ney Buxton ， President of the BOaRd</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Shop early Thursday morningâ€”Store closes at 1 clock.</t>
+          <t>L167: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1132,14 +1152,10 @@
           <t>L622: suspicious token(s): UManitoba (odd internal casing) :: UManitoba, Saskatchewan and Alberta,</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lady and gentleman â€” t</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L167: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L487: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • week,</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1173,12 +1189,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1195,14 +1211,10 @@
           <t>L712: suspicious token(s): seen1should (letter/digit mix) :: yes, I know him well. Haven't seen1should have to go back.</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | isolated marker/symbol line :: é—¨</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L172: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: I - ABORERSâ€™</t>
+          <t>L804: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1214,7 +1226,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1241,7 +1253,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1258,14 +1270,10 @@
           <t>L923: line starts with lowercase prefix glued to capitalized word | suspicious token(s): nJinternational (odd internal casing) | missing space after period :: nJinternational point of view.It assists to</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L361: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: t I to feel triumphantâ€”hap-</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WANTEDâ€”Four boys to sell papers. Ap-</t>
+          <t>L922: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: enjoying it for a few years and they •,</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1299,12 +1307,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1321,26 +1329,22 @@
           <t>L932: suspicious token(s): which1 (letter/digit mix) :: the outstanding characteristics which1'__</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>L393: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: d gentlemanâ€”the lady Italian,</t>
-        </is>
-      </c>
+      <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L186: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ply at Gleaner Office.â€”634d.</t>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 2</t>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1376,30 +1380,26 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>L761: suspicious token(s): BOaRd (odd internal casing) :: ney Buxton ï¼Œ President of the BOaRd</t>
+          <t>L761: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): BOaRd (odd internal casing) :: ney Buxton ， President of the BOaRd</t>
         </is>
       </c>
       <c r="I13" s="1" t="inlineStr"/>
-      <c r="J13" s="1" t="inlineStr">
-        <is>
-          <t>L432: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: one but fools â€” ourselves excepted</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L227: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FOR SALEâ€”Geo. Kitchen property about</t>
+          <t>L977: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: S'•</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: X</t>
+          <t>L41: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1439,21 +1439,13 @@
         </is>
       </c>
       <c r="I14" s="1" t="inlineStr"/>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L433: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: A. B. Kitchen.â€”613d.</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: B</t>
+          <t>L42: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1494,21 +1486,13 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Moncton, Aug. 4.â€” Emille Pellarin,</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€”DENTI STS. ------</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 2</t>
+          <t>L43: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1549,21 +1533,13 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DENTIST â€” Office and</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L287: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 419-11. House, 57-41.</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: Ã—</t>
+          <t>L51: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1604,21 +1580,13 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OFFICE AND RESIDENCEâ€”â€”</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | line starts with digit/letter garbage token | suspicious token(s): 0Photo (letter/digit mix) :: 0Photoâ€™s COPHRIETESLIN 6^</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 3</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+00D7 MULTIPLICATION SIGN | isolated marker/symbol line :: ×</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1647,26 +1615,18 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L614: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: glorious beauty â€” glorious in its youth</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L293: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: always with admirationâ€”or envy."</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: -</t>
+          <t>L56: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1690,21 +1650,13 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L615: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and freshnessâ€”and smiled.</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L297: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "Ought I to feel triumphantâ€”hap-</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 0</t>
+          <t>L61: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1733,21 +1685,13 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of his â€”"</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OFFICE AND RESIDENCE â€” Corner</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L69: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -1776,21 +1720,13 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L681: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " I understand.â€� he said, as if her</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L366: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: us during this weekâ€™s sale.</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: a</t>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -1819,21 +1755,13 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L738: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: suspicious. The expected happenedâ€”â€”</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L383: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: They are unapproachableâ€”even by</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L106: isolated marker/symbol line :: 7</t>
+          <t>L92: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -1862,21 +1790,13 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L757: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London, Aug. 4 â€” In view of Britain's</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L418: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and freshnessâ€”and smiled.</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: 3</t>
+          <t>L106: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -1905,21 +1825,13 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L781: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L456: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: will leave the oâ€™1 Star Line wharf.</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L147: isolated marker/symbol line :: s</t>
+          <t>L107: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -1949,16 +1861,12 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L458: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and Friday mornings at 8 oâ€™clock for St.</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L167: symbol-only separator/garbage line :: $12.00</t>
+          <t>L147: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -1988,16 +1896,12 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L487: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ week,</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L194: isolated marker/symbol line :: E.</t>
+          <t>L167: symbol-only separator/garbage line :: $12.00</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2027,16 +1931,12 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BOYâ€™S INJURIES</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L343: isolated marker/symbol line :: y.</t>
+          <t>L194: isolated marker/symbol line :: E.</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2066,16 +1966,12 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L527: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: something of Lord Dashleighâ€”every-</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | isolated marker/symbol line :: é—¨</t>
+          <t>L323: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。''</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2105,21 +2001,17 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: That isâ€”yes, it is Wilmot," said</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L354: isolated marker/symbol line :: L</t>
+          <t>L343: isolated marker/symbol line :: y.</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L167: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L167: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2144,16 +2036,12 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: know a way down to the bottom of the one but foolsâ€”ourselves excepted-</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L431: isolated marker/symbol line :: 1</t>
+          <t>L353: stray/suspicious non-ASCII glyph(s): U+95E8 CJK UNIFIED IDEOGRAPH-95E8 | isolated marker/symbol line :: 门</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2183,16 +2071,12 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: OFFICE â€” Opp. Officersâ€™ Quarters, Queen</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L433: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L354: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2222,16 +2106,12 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L604: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Moncton, Aug. 4.â€”Emilie Pellarin,</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L506: isolated marker/symbol line :: &amp;</t>
+          <t>L431: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
@@ -2261,16 +2141,12 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N B.â€” Unauthorized publication of this</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L507: isolated marker/symbol line :: &amp;</t>
+          <t>L433: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -2300,16 +2176,12 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: advertisement will not be paid for.â€”</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L511: isolated marker/symbol line :: T</t>
+          <t>L506: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -2339,16 +2211,12 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L680: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lady and gentlemanâ€”the lady Italian,</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L513: isolated marker/symbol line :: ,</t>
+          <t>L507: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -2378,16 +2246,12 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L686: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: illyâ€™s</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L514: isolated marker/symbol line :: ,</t>
+          <t>L511: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -2417,16 +2281,12 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L767: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: quite true, you know. But he went mind my leaving youâ€”. Oh, hereâ€™s a</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L522: isolated marker/symbol line :: H</t>
+          <t>L513: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
@@ -2456,16 +2316,12 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L773: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: find Gerald and tell him thatâ€”</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L524: isolated marker/symbol line :: B.</t>
+          <t>L514: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -2495,16 +2351,12 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L531: isolated marker/symbol line :: F.</t>
+          <t>L522: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
@@ -2534,16 +2386,12 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: hall; then he looked up and saw her -------------â€”â€”</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L548: isolated marker/symbol line :: t</t>
+          <t>L524: isolated marker/symbol line :: B.</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
@@ -2573,21 +2421,17 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L855: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: "Charlie" Foster, as he is familiar naments on skirtâ€”Maison Paquin,</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L555: isolated marker/symbol line :: C</t>
+          <t>L531: isolated marker/symbol line :: F.</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L804: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2612,16 +2456,12 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L859: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: I London, Aug. 4â€”In view of Britainâ€™s</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L591: symbol-only separator/garbage line :: 30690.</t>
+          <t>L548: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
@@ -2651,16 +2491,12 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L906: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Canadian Pacific at St. John,â€™ and in</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L631: isolated marker/symbol line :: '</t>
+          <t>L555: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
@@ -2690,16 +2526,12 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L913: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: resting place of the C. P. R.â€™s best</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L637: isolated marker/symbol line :: '</t>
+          <t>L591: symbol-only separator/garbage line :: 30690.</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
@@ -2729,21 +2561,17 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L922: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: enjoying it for a few years and they â€¢,</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L655: isolated marker/symbol line :: S</t>
+          <t>L631: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2768,21 +2596,17 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L956: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ask for Wilsonâ€™s, be sure</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L729: isolated marker/symbol line :: -</t>
+          <t>L637: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L983: isolated marker/symbol line :: I</t>
+          <t>L977: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: S'•</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -2807,19 +2631,19 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L774: isolated marker/symbol line :: ,</t>
-        </is>
-      </c>
-      <c r="O47" s="1" t="inlineStr"/>
+          <t>L655: isolated marker/symbol line :: S</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr">
+        <is>
+          <t>L983: isolated marker/symbol line :: I</t>
+        </is>
+      </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr"/>
       <c r="R47" s="1" t="inlineStr"/>
@@ -2842,16 +2666,12 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L977: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: S'â€¢</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L776: isolated marker/symbol line :: .</t>
+          <t>L729: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2882,7 +2702,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L781: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ã€�</t>
+          <t>L774: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2913,7 +2733,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L782: isolated marker/symbol line :: 2,</t>
+          <t>L776: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2944,7 +2764,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L803: isolated marker/symbol line :: 3</t>
+          <t>L781: isolated marker/symbol line :: 、</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2959,6 +2779,68 @@
       <c r="X51" s="1" t="inlineStr"/>
       <c r="Y51" s="1" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>L782: isolated marker/symbol line :: 2,</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="1" t="inlineStr"/>
+      <c r="C53" s="1" t="inlineStr"/>
+      <c r="D53" s="1" t="inlineStr"/>
+      <c r="E53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
+      <c r="H53" s="1" t="inlineStr"/>
+      <c r="I53" s="1" t="inlineStr"/>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
+      <c r="L53" s="1" t="inlineStr"/>
+      <c r="M53" s="1" t="inlineStr"/>
+      <c r="N53" s="1" t="inlineStr">
+        <is>
+          <t>L803: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr"/>
+      <c r="P53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr"/>
+      <c r="S53" s="1" t="inlineStr"/>
+      <c r="T53" s="1" t="inlineStr"/>
+      <c r="U53" s="1" t="inlineStr"/>
+      <c r="V53" s="1" t="inlineStr"/>
+      <c r="W53" s="1" t="inlineStr"/>
+      <c r="X53" s="1" t="inlineStr"/>
+      <c r="Y53" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
